--- a/backend/background_sentiment_analysis.xlsx
+++ b/backend/background_sentiment_analysis.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>4.34</v>
+        <v>4</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>

--- a/backend/background_sentiment_analysis.xlsx
+++ b/backend/background_sentiment_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C493"/>
+  <dimension ref="A1:C500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>1</v>
+        <v>1.49</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -7820,6 +7820,111 @@
         <v>4</v>
       </c>
       <c r="C493" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>2</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>2</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Middle Class</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>4</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Middle Class</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>4</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>2</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Middle Class</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>4</v>
+      </c>
+      <c r="C500" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
